--- a/fibre_analysis_output.xlsx
+++ b/fibre_analysis_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,316 +874,395 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1812222222222222</v>
+        <v>0.1019477222222222</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01793246743209137</v>
+        <v>0.02806571590533813</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1458888888888889</v>
+        <v>0.05956988888888887</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2101111111111111</v>
+        <v>0.1609652222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>321.9292714531197</v>
+        <v>262.2349577519491</v>
       </c>
       <c r="G6" t="n">
-        <v>46.12942604802129</v>
+        <v>95.83139734659412</v>
       </c>
       <c r="H6" t="n">
-        <v>230.0600840540321</v>
+        <v>142.7512275889141</v>
       </c>
       <c r="I6" t="n">
-        <v>414.0804550085159</v>
+        <v>429.7672182778938</v>
       </c>
       <c r="J6" t="n">
-        <v>14.32905614323387</v>
+        <v>36.54409700679268</v>
       </c>
       <c r="K6" t="n">
-        <v>9.895291654740795</v>
+        <v>27.5295173777021</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>341.5299426664553</v>
+        <v>294.4214598098467</v>
       </c>
       <c r="N6" t="n">
-        <v>362.8538496905764</v>
+        <v>366.4463652708171</v>
       </c>
       <c r="O6" t="n">
-        <v>321.4591820845206</v>
+        <v>236.5530244310066</v>
       </c>
       <c r="P6" t="n">
-        <v>7.874640717792407</v>
+        <v>3.000674472344666</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.03848404409053</v>
+        <v>4.831077348550521</v>
       </c>
       <c r="R6" t="n">
-        <v>5.617616167820732</v>
+        <v>1.863776263421335</v>
       </c>
       <c r="S6" t="n">
-        <v>234.2175761558871</v>
+        <v>109.4173790282314</v>
       </c>
       <c r="T6" t="n">
-        <v>1.360231578947368</v>
+        <v>1.02264</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3568554345524118</v>
+        <v>0.3159439725295892</v>
       </c>
       <c r="V6" t="n">
-        <v>29.20044100328285</v>
+        <v>29.59462872760919</v>
       </c>
       <c r="W6" t="n">
-        <v>2.70308564432637</v>
+        <v>7.654014898946032</v>
       </c>
       <c r="X6" t="n">
-        <v>26.23490294414195</v>
+        <v>30.89493590409031</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.25700281041124</v>
+        <v>25.86285156470137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.229375</v>
+        <v>0.1812222222222222</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02271454152795949</v>
+        <v>0.01793246743209137</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2026666666666667</v>
+        <v>0.1458888888888889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2695555555555555</v>
+        <v>0.2101111111111111</v>
       </c>
       <c r="F7" t="n">
-        <v>231.6500536459821</v>
+        <v>321.9292714531197</v>
       </c>
       <c r="G7" t="n">
-        <v>54.91333296088788</v>
+        <v>46.12942604802129</v>
       </c>
       <c r="H7" t="n">
-        <v>148.42154728971</v>
+        <v>230.0600840540321</v>
       </c>
       <c r="I7" t="n">
-        <v>303.3232514860957</v>
+        <v>414.0804550085159</v>
       </c>
       <c r="J7" t="n">
-        <v>23.7052968892504</v>
+        <v>14.32905614323387</v>
       </c>
       <c r="K7" t="n">
-        <v>9.902797396385608</v>
+        <v>9.895291654740795</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
-        <v>253.5339625576554</v>
+        <v>341.5299426664553</v>
       </c>
       <c r="N7" t="n">
-        <v>300.1600884723132</v>
+        <v>362.8538496905764</v>
       </c>
       <c r="O7" t="n">
-        <v>214.1506237466203</v>
+        <v>321.4591820845206</v>
       </c>
       <c r="P7" t="n">
-        <v>4.370722856273517</v>
+        <v>7.874640717792407</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.861448503708708</v>
+        <v>11.03848404409053</v>
       </c>
       <c r="R7" t="n">
-        <v>2.429987079014715</v>
+        <v>5.617616167820732</v>
       </c>
       <c r="S7" t="n">
-        <v>128.5003529794584</v>
+        <v>234.2175761558871</v>
       </c>
       <c r="T7" t="n">
-        <v>1.16765</v>
+        <v>1.360231578947368</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3615817591796199</v>
+        <v>0.3568554345524118</v>
       </c>
       <c r="V7" t="n">
-        <v>25.41860227555073</v>
+        <v>29.20044100328285</v>
       </c>
       <c r="W7" t="n">
-        <v>2.439075284771629</v>
+        <v>2.70308564432637</v>
       </c>
       <c r="X7" t="n">
-        <v>30.96662177704105</v>
+        <v>26.23490294414195</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.59563101987591</v>
+        <v>9.25700281041124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3024912280701755</v>
+        <v>0.229375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02889915097384144</v>
+        <v>0.02271454152795949</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2511111111111111</v>
+        <v>0.2026666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3657777777777778</v>
+        <v>0.2695555555555555</v>
       </c>
       <c r="F8" t="n">
-        <v>233.3046299789876</v>
+        <v>231.6500536459821</v>
       </c>
       <c r="G8" t="n">
-        <v>37.15536440938772</v>
+        <v>54.91333296088788</v>
       </c>
       <c r="H8" t="n">
-        <v>172.5419493131833</v>
+        <v>148.42154728971</v>
       </c>
       <c r="I8" t="n">
-        <v>299.1806953288255</v>
+        <v>303.3232514860957</v>
       </c>
       <c r="J8" t="n">
-        <v>15.92568669243045</v>
+        <v>23.7052968892504</v>
       </c>
       <c r="K8" t="n">
-        <v>9.553715378198364</v>
+        <v>9.902797396385608</v>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>248.8597278197844</v>
+        <v>253.5339625576554</v>
       </c>
       <c r="N8" t="n">
-        <v>266.1408330225629</v>
+        <v>300.1600884723132</v>
       </c>
       <c r="O8" t="n">
-        <v>232.7007224978768</v>
+        <v>214.1506237466203</v>
       </c>
       <c r="P8" t="n">
-        <v>7.079256509416166</v>
+        <v>4.370722856273517</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.01760915119143</v>
+        <v>7.861448503708708</v>
       </c>
       <c r="R8" t="n">
-        <v>5.002777805535633</v>
+        <v>2.429987079014715</v>
       </c>
       <c r="S8" t="n">
-        <v>163.583936740707</v>
+        <v>128.5003529794584</v>
       </c>
       <c r="T8" t="n">
-        <v>1.820252631578947</v>
+        <v>1.16765</v>
       </c>
       <c r="U8" t="n">
-        <v>0.441002679972231</v>
+        <v>0.3615817591796199</v>
       </c>
       <c r="V8" t="n">
-        <v>17.95502003555078</v>
+        <v>25.41860227555073</v>
       </c>
       <c r="W8" t="n">
-        <v>2.044232555680449</v>
+        <v>2.439075284771629</v>
       </c>
       <c r="X8" t="n">
-        <v>24.22755349018178</v>
+        <v>30.96662177704105</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.38529810400037</v>
+        <v>9.59563101987591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3024912280701755</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02889915097384144</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2511111111111111</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3657777777777778</v>
+      </c>
+      <c r="F9" t="n">
+        <v>233.3046299789876</v>
+      </c>
+      <c r="G9" t="n">
+        <v>37.15536440938772</v>
+      </c>
+      <c r="H9" t="n">
+        <v>172.5419493131833</v>
+      </c>
+      <c r="I9" t="n">
+        <v>299.1806953288255</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.92568669243045</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.553715378198364</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M9" t="n">
+        <v>248.8597278197844</v>
+      </c>
+      <c r="N9" t="n">
+        <v>266.1408330225629</v>
+      </c>
+      <c r="O9" t="n">
+        <v>232.7007224978768</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.079256509416166</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.01760915119143</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.002777805535633</v>
+      </c>
+      <c r="S9" t="n">
+        <v>163.583936740707</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.820252631578947</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.441002679972231</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17.95502003555078</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.044232555680449</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24.22755349018178</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.38529810400037</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0.3590201065011612</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>0.06642947158209415</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>0.2988888888888889</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>0.4418538881768926</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>166.0177140491317</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>56.97044445833979</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>95.57025253573281</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>228.4330970314423</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>34.31588296745238</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>18.50299478474454</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>187.2150349556951</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>261.5786998080872</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O10" t="n">
         <v>133.9920618122841</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" t="n">
         <v>2.852875557438051</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>6.04123289887048</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1.347224826864263</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>66.09774053634418</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>0.7713599999999999</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>0.3030782869161036</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V10" t="n">
         <v>27.60739652580063</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W10" t="n">
         <v>3.910849322327261</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X10" t="n">
         <v>39.291418652264</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y10" t="n">
         <v>14.16594758825722</v>
       </c>
     </row>

--- a/fibre_analysis_output.xlsx
+++ b/fibre_analysis_output.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,213 +417,213 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>series</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fracture_diameter_mean</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fracture_diameter_std</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fracture_diameter_min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fracture_diameter_max</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>fracture_stress_mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fracture_stress_std</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fracture_stress_min</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fracture_stress_max</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>fracture_stress_CV</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>fracture_diameter_CV</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>valid_samples</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>char_strength</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>char_strength_95%_upper</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>char_strength_95%_lower</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weibull_modulus</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>weibull_modulus_95%_upper</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>weibull_modulus_95%_lower</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Design Strength</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>%_elong_at_break_mean</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>%_elong_at_break_std</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>elastic_mod_mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>elastic_mod_std</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>%_elong_at_break_CV</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>elastic_mod_CV</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03695767195767195</v>
+        <v>0.0382283950617284</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006039732251288506</v>
+        <v>0.00340200979136033</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021</v>
+        <v>0.03177777777777778</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0441111111111111</v>
+        <v>0.043</v>
       </c>
       <c r="F2" t="n">
-        <v>376.9733499648798</v>
+        <v>303.7863978712435</v>
       </c>
       <c r="G2" t="n">
-        <v>213.7256573192341</v>
+        <v>74.29001961221891</v>
       </c>
       <c r="H2" t="n">
         <v>162.9236185483248</v>
       </c>
       <c r="I2" t="n">
-        <v>1059.120207464366</v>
+        <v>444.1206959773007</v>
       </c>
       <c r="J2" t="n">
-        <v>56.69516355443841</v>
+        <v>24.45468925955859</v>
       </c>
       <c r="K2" t="n">
-        <v>16.34229628480355</v>
+        <v>8.8991698078536</v>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>425.4517962070469</v>
+        <v>332.7131112941477</v>
       </c>
       <c r="N2" t="n">
-        <v>519.1213204111323</v>
+        <v>371.3166699715636</v>
       </c>
       <c r="O2" t="n">
-        <v>348.6838697983881</v>
+        <v>298.1229322009957</v>
       </c>
       <c r="P2" t="n">
-        <v>2.389879194494118</v>
+        <v>4.43075571187592</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.118636474114766</v>
+        <v>6.403413217309907</v>
       </c>
       <c r="R2" t="n">
-        <v>1.831416585960723</v>
+        <v>3.065801864114023</v>
       </c>
       <c r="S2" t="n">
-        <v>122.7720416296917</v>
+        <v>170.1911094754505</v>
       </c>
       <c r="T2" t="n">
-        <v>1.211428571428572</v>
+        <v>1.146666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3068922565703754</v>
+        <v>0.260022623450119</v>
       </c>
       <c r="V2" t="n">
-        <v>30.59325496512251</v>
+        <v>26.61080203807613</v>
       </c>
       <c r="W2" t="n">
-        <v>13.02451424826915</v>
+        <v>4.40955448277199</v>
       </c>
       <c r="X2" t="n">
-        <v>25.3330872168942</v>
+        <v>22.67639157995224</v>
       </c>
       <c r="Y2" t="n">
-        <v>42.57315628270871</v>
+        <v>16.5705433322249</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -714,165 +702,165 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>S2</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05855555555555556</v>
+        <v>0.05987795424673761</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009834545950455846</v>
+        <v>0.006722185919115795</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04588888888888888</v>
+        <v>0.05356609199650317</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07733333333333332</v>
+        <v>0.07196434293499931</v>
       </c>
       <c r="F4" t="n">
-        <v>243.9428739752721</v>
+        <v>216.4785925860338</v>
       </c>
       <c r="G4" t="n">
-        <v>93.24873507095933</v>
+        <v>71.08543452508471</v>
       </c>
       <c r="H4" t="n">
-        <v>155.1214344346931</v>
+        <v>118.0146446475014</v>
       </c>
       <c r="I4" t="n">
-        <v>472.9718189898531</v>
+        <v>303.343007889991</v>
       </c>
       <c r="J4" t="n">
-        <v>38.22564420570521</v>
+        <v>32.83716587210981</v>
       </c>
       <c r="K4" t="n">
-        <v>16.79523976358684</v>
+        <v>11.22647893315768</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>274.8378318457077</v>
+        <v>242.6515451195811</v>
       </c>
       <c r="N4" t="n">
-        <v>336.0192458786356</v>
+        <v>320.9393950415087</v>
       </c>
       <c r="O4" t="n">
-        <v>224.7961530183653</v>
+        <v>183.4607195582982</v>
       </c>
       <c r="P4" t="n">
-        <v>3.03465698599744</v>
+        <v>3.070103494869675</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.477862963639001</v>
+        <v>5.977410353724599</v>
       </c>
       <c r="R4" t="n">
-        <v>2.056593311908572</v>
+        <v>1.576859360732667</v>
       </c>
       <c r="S4" t="n">
-        <v>103.2778649758731</v>
+        <v>92.21923662762649</v>
       </c>
       <c r="T4" t="n">
-        <v>0.96</v>
+        <v>1.026853983333333</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3519555757091047</v>
+        <v>0.1973079193964238</v>
       </c>
       <c r="V4" t="n">
-        <v>25.9620057448105</v>
+        <v>21.15681431913626</v>
       </c>
       <c r="W4" t="n">
-        <v>5.338034484158689</v>
+        <v>4.22771062455969</v>
       </c>
       <c r="X4" t="n">
-        <v>36.66203913636507</v>
+        <v>19.2147980724514</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.56094793533315</v>
+        <v>19.98273729110409</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>F2</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05987795424673761</v>
+        <v>0.061</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006722185919115795</v>
+        <v>0.008850534537033392</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05356609199650317</v>
+        <v>0.04677777777777777</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07196434293499931</v>
+        <v>0.07733333333333332</v>
       </c>
       <c r="F5" t="n">
-        <v>216.4785925860338</v>
+        <v>226.4841556356066</v>
       </c>
       <c r="G5" t="n">
-        <v>71.08543452508471</v>
+        <v>64.27576093372183</v>
       </c>
       <c r="H5" t="n">
-        <v>118.0146446475014</v>
+        <v>155.1214344346931</v>
       </c>
       <c r="I5" t="n">
-        <v>303.343007889991</v>
+        <v>366.1675173759609</v>
       </c>
       <c r="J5" t="n">
-        <v>32.83716587210981</v>
+        <v>28.37980465050101</v>
       </c>
       <c r="K5" t="n">
-        <v>11.22647893315768</v>
+        <v>14.50907301153015</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>242.6515451195811</v>
+        <v>250.5789486128591</v>
       </c>
       <c r="N5" t="n">
-        <v>320.9393950415087</v>
+        <v>296.9254961128423</v>
       </c>
       <c r="O5" t="n">
-        <v>183.4607195582982</v>
+        <v>211.4665473660217</v>
       </c>
       <c r="P5" t="n">
-        <v>3.070103494869675</v>
+        <v>3.899642328454027</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.977410353724599</v>
+        <v>6.083075382895143</v>
       </c>
       <c r="R5" t="n">
-        <v>1.576859360732667</v>
+        <v>2.499921393811943</v>
       </c>
       <c r="S5" t="n">
-        <v>92.21923662762649</v>
+        <v>116.9931817445288</v>
       </c>
       <c r="T5" t="n">
-        <v>1.026853983333333</v>
+        <v>0.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1973079193964238</v>
+        <v>0.29698484809835</v>
       </c>
       <c r="V5" t="n">
-        <v>21.15681431913626</v>
+        <v>25.94113689933733</v>
       </c>
       <c r="W5" t="n">
-        <v>4.22771062455969</v>
+        <v>5.70463317969782</v>
       </c>
       <c r="X5" t="n">
-        <v>19.2147980724514</v>
+        <v>32.99831645537222</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.98273729110409</v>
+        <v>21.99068299062693</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -951,7 +939,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
@@ -1030,7 +1018,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>X1</t>
         </is>
@@ -1109,7 +1097,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
@@ -1188,7 +1176,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
